--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487141_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487141_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2744</v>
+        <v>7.8834</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2965</v>
+        <v>7.655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.978</v>
+        <v>0.2284</v>
       </c>
       <c r="G2" t="n">
         <v>7.0925</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3822</v>
+        <v>0.9911</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5692</v>
+        <v>0.9277</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.0634</v>
       </c>
       <c r="V2" t="n">
         <v>0.5717</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3321</v>
+        <v>6.4124</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3884</v>
+        <v>4.1475</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9437</v>
+        <v>2.265</v>
       </c>
       <c r="G3" t="n">
         <v>3.7348</v>
@@ -688,13 +688,13 @@
         <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3464</v>
+        <v>0.4267</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3326</v>
+        <v>1.0917</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9862</v>
+        <v>-0.665</v>
       </c>
       <c r="V3" t="n">
         <v>0.8999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3842</v>
+        <v>3.5974</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5716</v>
+        <v>1.7312</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8126</v>
+        <v>1.8662</v>
       </c>
       <c r="G4" t="n">
         <v>0.8885</v>
@@ -766,13 +766,13 @@
         <v>2.7021</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2763</v>
+        <v>-0.0631</v>
       </c>
       <c r="T4" t="n">
-        <v>0.16</v>
+        <v>0.3196</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4363</v>
+        <v>-0.3828</v>
       </c>
       <c r="V4" t="n">
         <v>1.228</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4799</v>
+        <v>0.4868</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0557</v>
+        <v>-0.1558</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5356</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8381</v>
@@ -844,13 +844,13 @@
         <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>0.546</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6821</v>
+        <v>0.582</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1362</v>
+        <v>-0.0291</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8132</v>
+        <v>-0.366</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3877</v>
+        <v>-0.1279</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4255</v>
+        <v>-0.2381</v>
       </c>
       <c r="G6" t="n">
         <v>-2.8539</v>
@@ -922,13 +922,13 @@
         <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4105</v>
+        <v>0.0367</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5169</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9274</v>
+        <v>-0.74</v>
       </c>
       <c r="V6" t="n">
         <v>0.3281</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0126</v>
+        <v>-0.6924</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5173</v>
+        <v>-1.1167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5046</v>
+        <v>0.4243</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2243</v>
@@ -1000,13 +1000,13 @@
         <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09719999999999999</v>
+        <v>0.2231</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0304</v>
+        <v>0.3702</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0668</v>
+        <v>-0.1471</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6562</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3098</v>
+        <v>-0.8878</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3013</v>
+        <v>-0.854</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0339</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0743</v>
+        <v>-1.2696</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2143</v>
+        <v>-0.4099</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.14</v>
+        <v>-0.8597</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0207</v>
+        <v>-0.5091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>0.1913</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.7004</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0536</v>
+        <v>-0.7604</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1936</v>
+        <v>-0.6012</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.14</v>
+        <v>-0.1592</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9301</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-2.3161</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>0.546</v>
+        <v>0.6676</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6081</v>
+        <v>0.4574</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0621</v>
+        <v>0.2102</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3479</v>
+        <v>-1.6033</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.314</v>
+        <v>-1.7018</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0339</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2696</v>
+        <v>0.0743</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4099</v>
+        <v>0.2143</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8597</v>
+        <v>-0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5091</v>
+        <v>0.0207</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1913</v>
+        <v>0.0207</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7004</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7604</v>
+        <v>0.0536</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6012</v>
+        <v>0.1936</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1592</v>
+        <v>-0.14</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3161</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3161</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="T9" t="n">
         <v>0.2076</v>
       </c>
-      <c r="T9" t="n">
-        <v>-0.0026</v>
-      </c>
       <c r="U9" t="n">
-        <v>0.2102</v>
+        <v>0.0449</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0503</v>
+        <v>-1.8768</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4221</v>
+        <v>-1.2218</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6283</v>
+        <v>-0.655</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0733</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0469</v>
+        <v>0.1266</v>
       </c>
       <c r="T10" t="n">
-        <v>0.074</v>
+        <v>0.2743</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.121</v>
+        <v>-0.1477</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8513</v>
+        <v>-2.535</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3085</v>
+        <v>-3.5593</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1598</v>
+        <v>1.0243</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2668</v>
+        <v>-1.0544</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7131</v>
+        <v>-1.1551</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4463</v>
+        <v>0.1007</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1413</v>
+        <v>-1.2753</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4088</v>
+        <v>-1.1282</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7326</v>
+        <v>-0.1471</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4082</v>
+        <v>0.2209</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1219</v>
+        <v>-0.0268</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2863</v>
+        <v>0.2478</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3503</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3252</v>
+        <v>-0.3539</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0251</v>
+        <v>-0.1616</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9693</v>
+        <v>-3.005</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8597</v>
+        <v>0.2084</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8905</v>
+        <v>-3.2134</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0544</v>
+        <v>-0.2668</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1551</v>
+        <v>-0.7131</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1007</v>
+        <v>0.4463</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2753</v>
+        <v>1.1413</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1282</v>
+        <v>0.4088</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1471</v>
+        <v>0.7326</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2209</v>
+        <v>-1.4082</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0268</v>
+        <v>-1.1219</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2478</v>
+        <v>-0.2863</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9301</v>
+        <v>-1.158</v>
       </c>
       <c r="R12" t="n">
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9498</v>
+        <v>0.1966</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6544</v>
+        <v>0.2251</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2955</v>
+        <v>-0.0284</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.116200000000001</v>
+        <v>7.4137</v>
       </c>
       <c r="E13" t="n">
-        <v>4.707199999999998</v>
+        <v>5.0048</v>
       </c>
       <c r="F13" t="n">
-        <v>2.408999999999999</v>
+        <v>2.409</v>
       </c>
       <c r="G13" t="n">
         <v>4.209700000000001</v>
@@ -1459,7 +1459,7 @@
         <v>1.7778</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9651000000000004</v>
+        <v>0.9651000000000005</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.4057</v>
@@ -1468,10 +1468,10 @@
         <v>17.3705</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5978</v>
+        <v>2.8951</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5807</v>
+        <v>4.878400000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-1.9832</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5224</v>
+        <v>2.6406</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4638</v>
+        <v>3.6626</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9414</v>
+        <v>-1.022</v>
       </c>
       <c r="G14" t="n">
         <v>1.2752</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4449</v>
+        <v>0.5632</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8667</v>
+        <v>1.0656</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4217</v>
+        <v>-0.5024</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5138</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0442</v>
+        <v>1.865</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5754</v>
+        <v>0.6741</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4688</v>
+        <v>1.1909</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1542</v>
@@ -1624,13 +1624,13 @@
         <v>2.8951</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.0859</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5692</v>
+        <v>0.668</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.476</v>
+        <v>-0.7539</v>
       </c>
       <c r="V15" t="n">
         <v>2.3331</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8007</v>
+        <v>0.8683</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7542</v>
+        <v>-0.2076</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0465</v>
+        <v>1.0759</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6886</v>
+        <v>2.0371</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0449</v>
+        <v>-1.2988</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3563</v>
+        <v>3.3359</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9301</v>
+        <v>1.9835</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7294</v>
+        <v>-0.5641</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.7993</v>
+        <v>2.5476</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2415</v>
+        <v>0.0536</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6845</v>
+        <v>-0.7347</v>
       </c>
       <c r="O16" t="n">
-        <v>1.443</v>
+        <v>0.7883</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.4741</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.9833</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2531</v>
+        <v>-0.66</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0656</v>
+        <v>-0.2611</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8124</v>
+        <v>-0.3989</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3331</v>
+        <v>-0.1228</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7418</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4087</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2136</v>
+        <v>0.767</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4079</v>
+        <v>0.4538</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.3132</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0371</v>
+        <v>1.6886</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2988</v>
+        <v>2.0449</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3359</v>
+        <v>-0.3563</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9835</v>
+        <v>2.9301</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5641</v>
+        <v>4.7294</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5476</v>
+        <v>-1.7993</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0536</v>
+        <v>-1.2415</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7347</v>
+        <v>-2.6845</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7883</v>
+        <v>1.443</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.386</v>
+        <v>-3.4741</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-5.9833</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>2.5091</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3147</v>
+        <v>0.2194</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4614</v>
+        <v>0.7651</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8534</v>
+        <v>-0.5457</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1228</v>
+        <v>2.3331</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.7418</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1228</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7342</v>
+        <v>-0.6073</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0576</v>
+        <v>0.0426</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6766</v>
+        <v>-0.6498</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6925</v>
@@ -1858,13 +1858,13 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2346</v>
+        <v>-0.1077</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4455</v>
+        <v>-0.9111</v>
       </c>
       <c r="E19" t="n">
         <v>1.0965</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5419</v>
+        <v>-2.0075</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2445</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9802</v>
+        <v>-0.4458</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3291</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6511</v>
+        <v>-0.1167</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1857</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0104</v>
+        <v>-3.0704</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4405</v>
+        <v>-1.339</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5698</v>
+        <v>-1.7314</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4107</v>
@@ -2014,13 +2014,13 @@
         <v>2.3161</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7278</v>
+        <v>0.2122</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0562</v>
+        <v>0.0453</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3285</v>
+        <v>0.1669</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0649</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.507</v>
+        <v>-6.6656</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.3928</v>
+        <v>-6.7919</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1143</v>
+        <v>0.1263</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7086</v>
@@ -2092,13 +2092,13 @@
         <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1316</v>
+        <v>-0.2902</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5525</v>
+        <v>0.0483</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.3385</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.116199999999999</v>
+        <v>-5.1135</v>
       </c>
       <c r="E22" t="n">
         <v>-2.408900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.7072</v>
+        <v>-2.7044</v>
       </c>
       <c r="G22" t="n">
         <v>-4.209599999999998</v>
@@ -2170,13 +2170,13 @@
         <v>16.4057</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.5977</v>
+        <v>-0.5947999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.983300000000001</v>
+        <v>1.9833</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.5809</v>
+        <v>-2.5781</v>
       </c>
       <c r="V22" t="n">
         <v>0.6562000000000001</v>
